--- a/95 Файлы/Допуск. Кампус/Допуск. Кампус. Допуск. Кампус. СК МЛС.xlsx
+++ b/95 Файлы/Допуск. Кампус/Допуск. Кампус. Допуск. Кампус. СК МЛС.xlsx
@@ -234,7 +234,7 @@
     <t>Т035ЕА159</t>
   </si>
   <si>
-    <t>с 1.04.2026 по 30.04.2026</t>
+    <t>с 1.05.2026 по 31.05.2026</t>
   </si>
 </sst>
 </file>
@@ -444,6 +444,36 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -462,12 +492,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -476,30 +500,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -808,128 +808,128 @@
       </c>
     </row>
     <row r="2" spans="2:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
     </row>
     <row r="3" spans="2:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="F3" s="40" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="F3" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
     </row>
     <row r="4" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="5" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
     </row>
     <row r="7" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
     </row>
     <row r="8" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="2:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
     </row>
     <row r="11" spans="2:11" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
@@ -941,18 +941,18 @@
       <c r="D11" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41" t="s">
+      <c r="F11" s="24"/>
+      <c r="G11" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41" t="s">
+      <c r="H11" s="24"/>
+      <c r="I11" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="J11" s="41"/>
+      <c r="J11" s="24"/>
       <c r="K11" s="7" t="s">
         <v>36</v>
       </c>
@@ -1088,53 +1088,53 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
       <c r="K17" s="17"/>
     </row>
     <row r="18" spans="1:11" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="28"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="27" t="s">
+      <c r="D18" s="38"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="27" t="s">
+      <c r="G18" s="38"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="J18" s="29"/>
+      <c r="J18" s="39"/>
       <c r="K18" s="17"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <v>1</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="31"/>
+      <c r="D19" s="26"/>
       <c r="E19" s="19"/>
-      <c r="F19" s="30" t="s">
+      <c r="F19" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="G19" s="31"/>
-      <c r="H19" s="32"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="40"/>
       <c r="I19" s="6" t="s">
         <v>23</v>
       </c>
@@ -1147,16 +1147,16 @@
       <c r="B20" s="18">
         <v>2</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="31"/>
+      <c r="D20" s="26"/>
       <c r="E20" s="19"/>
-      <c r="F20" s="30" t="s">
+      <c r="F20" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="31"/>
-      <c r="H20" s="32"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="40"/>
       <c r="I20" s="6" t="s">
         <v>22</v>
       </c>
@@ -1169,16 +1169,16 @@
       <c r="B21" s="18">
         <v>3</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="31"/>
+      <c r="D21" s="26"/>
       <c r="E21" s="19"/>
-      <c r="F21" s="30" t="s">
+      <c r="F21" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="31"/>
-      <c r="H21" s="32"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="40"/>
       <c r="I21" s="6" t="s">
         <v>30</v>
       </c>
@@ -1191,16 +1191,16 @@
       <c r="B22" s="21">
         <v>4</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="31"/>
+      <c r="D22" s="26"/>
       <c r="E22" s="22"/>
-      <c r="F22" s="42" t="s">
+      <c r="F22" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
       <c r="I22" s="23"/>
       <c r="J22" s="23" t="s">
         <v>65</v>
@@ -1209,26 +1209,26 @@
     </row>
     <row r="23" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
       <c r="G23" s="15"/>
-      <c r="H23" s="34" t="s">
+      <c r="H23" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
       <c r="K23" s="17"/>
     </row>
     <row r="24" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="25"/>
+      <c r="C24" s="35"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
@@ -1241,11 +1241,11 @@
       <c r="K24" s="17"/>
     </row>
     <row r="25" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="24">
+      <c r="B25" s="34">
         <f ca="1">TODAY()</f>
-        <v>46112</v>
-      </c>
-      <c r="C25" s="24"/>
+        <v>46140</v>
+      </c>
+      <c r="C25" s="34"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
@@ -1257,11 +1257,20 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="F9:J9"/>
     <mergeCell ref="F10:J10"/>
@@ -1278,20 +1287,11 @@
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="F3:J3"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="F22:H22"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.55118110236220474" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="98" fitToHeight="0" orientation="portrait" r:id="rId1"/>
